--- a/design_tables/excel/Enemy.xlsx
+++ b/design_tables/excel/Enemy.xlsx
@@ -16,7 +16,6 @@
     <sheet name="Enemy" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -202,22 +201,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EnemyTable" displayName="EnemyTable" ref="A1:H4">
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="name"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="max_hp"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="init_magic_shield"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="action_ids"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ai_mode"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="ai_script_path"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="comment"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -527,8 +510,10 @@
       <c r="I4" t="s">
         <v>35</v>
       </c>
-      <c r="J4" t="s">
-        <v>36</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>enemy_corrupted_student_battle.png</t>
+        </is>
       </c>
       <c r="K4" t="s">
         <v>37</v>
@@ -543,8 +528,5 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>